--- a/game_config/Datas/SkillConfig.xlsx
+++ b/game_config/Datas/SkillConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitee\TiangZ\game_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D54DC0E-1300-4242-842A-3199B5DB7803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C07B8B1-A3EB-4DA9-BAB1-7B0C4A16762A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{4FEA86BE-AAC9-482E-9640-5202A476D250}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="23040" windowHeight="12120" xr2:uid="{4FEA86BE-AAC9-482E-9640-5202A476D250}"/>
   </bookViews>
   <sheets>
     <sheet name="SkillConfig" sheetId="1" r:id="rId1"/>
@@ -168,9 +168,6 @@
     <t>寒冰箭</t>
   </si>
   <si>
-    <t>读条1.5秒，15米弹道法术，造成50点冰霜伤害并刷新5秒冰冷。</t>
-  </si>
-  <si>
     <t>Enemy</t>
   </si>
   <si>
@@ -186,9 +183,6 @@
     <t>火焰冲击</t>
   </si>
   <si>
-    <t>瞬发，5米，12秒冷却；造成100点火焰伤害，并按施法者刷新6秒灼烧。</t>
-  </si>
-  <si>
     <t>Direct</t>
   </si>
   <si>
@@ -198,9 +192,6 @@
     <t>惩击</t>
   </si>
   <si>
-    <t>读条1.5秒，15米直接命中，造成60点神圣伤害。</t>
-  </si>
-  <si>
     <t>真言术·盾</t>
   </si>
   <si>
@@ -217,6 +208,18 @@
   </si>
   <si>
     <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>读条1.5秒，30米弹道法术，造成50点冰霜伤害并刷新5秒冰冷。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>瞬发，10米，12秒冷却；造成100点火焰伤害，并按施法者刷新6秒灼烧。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>读条1.5秒，30米直接命中，造成60点神圣伤害。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -713,7 +716,7 @@
         <v>23</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -819,10 +822,10 @@
         <v>42</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="F5" s="2">
         <v>1500</v>
@@ -834,19 +837,19 @@
         <v>1000</v>
       </c>
       <c r="I5" s="2">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K5" s="2">
         <v>20</v>
       </c>
       <c r="L5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M5" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="N5" s="2" t="b">
         <v>1</v>
@@ -861,13 +864,13 @@
         <v>3002</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F6" s="2">
         <v>0</v>
@@ -879,19 +882,19 @@
         <v>1000</v>
       </c>
       <c r="I6" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K6" s="2">
         <v>0</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N6" s="2" t="b">
         <v>1</v>
@@ -906,13 +909,13 @@
         <v>3003</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F7" s="2">
         <v>1500</v>
@@ -924,19 +927,19 @@
         <v>1000</v>
       </c>
       <c r="I7" s="2">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K7" s="2">
         <v>0</v>
       </c>
       <c r="L7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M7" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="N7" s="2" t="b">
         <v>1</v>
@@ -951,13 +954,13 @@
         <v>3004</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F8" s="2">
         <v>0</v>
@@ -972,16 +975,16 @@
         <v>15</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K8" s="2">
         <v>0</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N8" s="2" t="b">
         <v>1</v>
@@ -996,13 +999,13 @@
         <v>3005</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F9" s="2">
         <v>0</v>
@@ -1017,16 +1020,16 @@
         <v>15</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K9" s="2">
         <v>0</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N9" s="2" t="b">
         <v>1</v>

--- a/game_config/Datas/SkillConfig.xlsx
+++ b/game_config/Datas/SkillConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitee\TiangZ\game_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7817B45-7608-40FC-A915-A74444EB0E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1CF3900-CFCC-4F48-A333-BB31F40D6242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SkillConfig" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="75">
   <si>
     <t>##var</t>
   </si>
@@ -220,12 +220,6 @@
   </si>
   <si>
     <t>引导总跳数（非引导填0）</t>
-  </si>
-  <si>
-    <t>引导治疗</t>
-  </si>
-  <si>
-    <t>引导3秒，每秒恢复30点生命；移动会打断引导。</t>
   </si>
   <si>
     <t>精神鞭笞</t>
@@ -249,6 +243,22 @@
   </si>
   <si>
     <t>ResetOnStart</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>瞬发，为自己添加持续24秒的恢复Buff，每3秒恢复10点生命，共8次。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Friendly</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Allow</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1069,16 +1079,16 @@
         <v>3006</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="F10">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="G10">
         <v>6000</v>
@@ -1090,16 +1100,16 @@
         <v>15</v>
       </c>
       <c r="J10" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="M10" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="N10" s="4" t="b">
         <v>1</v>
@@ -1111,10 +1121,10 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -1122,13 +1132,13 @@
         <v>3007</v>
       </c>
       <c r="C11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" t="s">
         <v>67</v>
-      </c>
-      <c r="D11" t="s">
-        <v>68</v>
-      </c>
-      <c r="E11" t="s">
-        <v>69</v>
       </c>
       <c r="F11">
         <v>5000</v>
@@ -1143,16 +1153,16 @@
         <v>30</v>
       </c>
       <c r="J11" t="s">
+        <v>68</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11" t="s">
+        <v>69</v>
+      </c>
+      <c r="M11" t="s">
         <v>70</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11" t="s">
-        <v>71</v>
-      </c>
-      <c r="M11" t="s">
-        <v>72</v>
       </c>
       <c r="N11" s="4">
         <v>1</v>
